--- a/Data/Clean/tabla_indices_mapas.xlsx
+++ b/Data/Clean/tabla_indices_mapas.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,17 +10,17 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B01992-E649-4E45-8097-70B2A5CBC103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="232" uniqueCount="97">
   <si>
     <t>encuesta_si</t>
   </si>
@@ -316,11 +316,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="1">
     <numFmt numFmtId="169" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -355,8 +355,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,7 +375,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -526,7 +526,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -550,9 +550,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -576,7 +576,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -611,7 +611,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -629,7 +629,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -654,7 +654,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -690,15 +690,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" bestFit="true" customWidth="true"/>
+    <col min="10" max="10" width="12.109375" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,7 +733,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -758,17 +758,17 @@
       <c r="H2" s="1">
         <v>3</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>4.6676060000000001</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>-74.054133999999991</v>
       </c>
       <c r="K2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -793,17 +793,17 @@
       <c r="H3" s="1">
         <v>3</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>4.6672186999999994</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>-74.054656800000004</v>
       </c>
       <c r="K3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -828,17 +828,17 @@
       <c r="H4" s="1">
         <v>3</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="1">
         <v>4.6143874999999994</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>-74.066146599999996</v>
       </c>
       <c r="K4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -863,17 +863,17 @@
       <c r="H5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="1">
         <v>4.6768090999999998</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>-74.047285700000003</v>
       </c>
       <c r="K5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -898,17 +898,17 @@
       <c r="H6" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="1">
         <v>4.6702380000000003</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>-74.053262000000004</v>
       </c>
       <c r="K6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -933,17 +933,17 @@
       <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="1">
         <v>4.6690924999999996</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>-74.053077899999991</v>
       </c>
       <c r="K7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -968,17 +968,17 @@
       <c r="H8" s="1">
         <v>3</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="1">
         <v>4.6144970000000001</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>-74.068920199999994</v>
       </c>
       <c r="K8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1003,17 +1003,17 @@
       <c r="H9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="1">
         <v>4.6963597000000004</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>-74.030839300000011</v>
       </c>
       <c r="K9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -1038,17 +1038,17 @@
       <c r="H10" s="1">
         <v>3</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="1">
         <v>4.6481026999999999</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>-74.057687899999991</v>
       </c>
       <c r="K10" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1073,17 +1073,17 @@
       <c r="H11" s="1">
         <v>3</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="1">
         <v>4.6693340000000001</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>-74.053410999999997</v>
       </c>
       <c r="K11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -1108,17 +1108,17 @@
       <c r="H12" s="1">
         <v>3</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="1">
         <v>4.6127433</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>-74.066767900000002</v>
       </c>
       <c r="K12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1143,17 +1143,17 @@
       <c r="H13" s="1">
         <v>2</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>4.6833840000000002</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>-74.060512199999991</v>
       </c>
       <c r="K13" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1178,17 +1178,17 @@
       <c r="H14" s="1">
         <v>2</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="1">
         <v>4.6676150999999999</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>-74.053812199999996</v>
       </c>
       <c r="K14" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1213,17 +1213,17 @@
       <c r="H15" s="1">
         <v>3</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="1">
         <v>4.6661218999999994</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>-74.055825599999991</v>
       </c>
       <c r="K15" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1248,17 +1248,17 @@
       <c r="H16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="1">
         <v>4.6868488000000008</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>-74.051691300000002</v>
       </c>
       <c r="K16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -1283,17 +1283,17 @@
       <c r="H17" s="1">
         <v>3</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="1">
         <v>4.6967935000000001</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>-74.030623399999996</v>
       </c>
       <c r="K17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -1318,17 +1318,17 @@
       <c r="H18" s="1">
         <v>2</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
         <v>4.6459815999999998</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>-74.059867300000008</v>
       </c>
       <c r="K18" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1353,17 +1353,17 @@
       <c r="H19" s="1">
         <v>3</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="1">
         <v>4.6521540999999997</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>-74.056230099999993</v>
       </c>
       <c r="K19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1388,17 +1388,17 @@
       <c r="H20" s="1">
         <v>2</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="1">
         <v>4.6764162999999996</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>-74.048835699999998</v>
       </c>
       <c r="K20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -1423,17 +1423,17 @@
       <c r="H21" s="1">
         <v>3</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="1">
         <v>4.6946344</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>-74.032175100000018</v>
       </c>
       <c r="K21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -1458,17 +1458,17 @@
       <c r="H22" s="1">
         <v>2</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="1">
         <v>4.6318294999999994</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>-74.072424699999999</v>
       </c>
       <c r="K22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -1493,17 +1493,17 @@
       <c r="H23" s="1">
         <v>2</v>
       </c>
-      <c r="I23" s="2">
-        <v>4.6560703999999999</v>
-      </c>
-      <c r="J23" s="2">
+      <c r="I23" s="1">
+        <v>4.6560704</v>
+      </c>
+      <c r="J23" s="1">
         <v>-74.054585199999991</v>
       </c>
       <c r="K23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1528,17 +1528,17 @@
       <c r="H24" s="1">
         <v>3</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
         <v>4.6944631000000001</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>-74.032353299999997</v>
       </c>
       <c r="K24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -1563,17 +1563,17 @@
       <c r="H25" s="1">
         <v>2</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <v>4.6810323999999994</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>-74.046398499999995</v>
       </c>
       <c r="K25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1598,17 +1598,17 @@
       <c r="H26" s="1">
         <v>2</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="1">
         <v>4.6963846</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>-74.044303599999992</v>
       </c>
       <c r="K26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -1633,17 +1633,17 @@
       <c r="H27" s="1">
         <v>2</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="1">
         <v>4.6674096</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>-74.071941100000004</v>
       </c>
       <c r="K27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -1668,17 +1668,17 @@
       <c r="H28" s="1">
         <v>1</v>
       </c>
-      <c r="I28" s="2">
-        <v>4.6130630999999997</v>
-      </c>
-      <c r="J28" s="2">
+      <c r="I28" s="1">
+        <v>4.6130630999999998</v>
+      </c>
+      <c r="J28" s="1">
         <v>-74.06663069999999</v>
       </c>
       <c r="K28" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1703,17 +1703,17 @@
       <c r="H29" s="1">
         <v>2</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="1">
         <v>4.6521447</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>-74.055869399999992</v>
       </c>
       <c r="K29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -1738,17 +1738,17 @@
       <c r="H30" s="1">
         <v>2</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="1">
         <v>4.6742881000000001</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>-74.048050799999999</v>
       </c>
       <c r="K30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1773,17 +1773,17 @@
       <c r="H31" s="1">
         <v>1</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="1">
         <v>4.6009235999999998</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>-74.07176849999999</v>
       </c>
       <c r="K31" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1808,17 +1808,17 @@
       <c r="H32" s="1">
         <v>1</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="1">
         <v>4.6645292999999999</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>-74.063854599999999</v>
       </c>
       <c r="K32" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -1843,17 +1843,17 @@
       <c r="H33" s="1">
         <v>2</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="1">
         <v>4.6509020999999997</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>-74.057391199999998</v>
       </c>
       <c r="K33" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -1878,17 +1878,17 @@
       <c r="H34" s="1">
         <v>2</v>
       </c>
-      <c r="I34" s="2">
-        <v>4.5965129999999998</v>
-      </c>
-      <c r="J34" s="2">
+      <c r="I34" s="1">
+        <v>4.5965129999999999</v>
+      </c>
+      <c r="J34" s="1">
         <v>-74.069208899999992</v>
       </c>
       <c r="K34" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -1913,17 +1913,17 @@
       <c r="H35" s="1">
         <v>1</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="1">
         <v>4.6574445999999998</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>-74.05652529999999</v>
       </c>
       <c r="K35" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1948,10 +1948,10 @@
       <c r="H36" s="1">
         <v>2</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="1">
         <v>4.6859608000000001</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>-74.054435400000003</v>
       </c>
       <c r="K36" t="s">
